--- a/supplementary/Data_S2.xlsx
+++ b/supplementary/Data_S2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seokm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0003F4FB-2AA6-4F2E-AFD3-BA0408258D78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5027735-667D-4451-B044-3026A17ACD3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11835" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="3855" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -1914,16 +1914,19 @@
       <sz val="18"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF16324F"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1937,50 +1940,59 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF16324F"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF16324F"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF374151"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2198,18 +2210,18 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2460,7 +2472,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="52"/>
@@ -2469,7 +2481,7 @@
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="51" t="s">
         <v>614</v>
       </c>
     </row>
@@ -2477,7 +2489,7 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="2" t="s">
         <v>615</v>
       </c>
     </row>
@@ -39728,12 +39740,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -62941,15 +62953,15 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="56" t="s">
         <v>567</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
     </row>
     <row r="14" spans="1:7" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="31" t="s">
